--- a/data/ground_truth/EMAS.xlsx
+++ b/data/ground_truth/EMAS.xlsx
@@ -92,7 +92,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,6 +124,7 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="59.6640625" customWidth="1" min="1" max="1"/>
@@ -630,16 +631,16 @@
           <t>Aset</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="19" t="n">
         <v>17220170107143</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="19" t="n">
         <v>13717107593220</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>12343970133333</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>11679883344262</v>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -671,16 +672,16 @@
           <t>total aset lancar</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>2203440732143</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>1432792796610</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>1020518550000</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>1414905311475</v>
       </c>
       <c r="F5" s="18" t="n"/>
@@ -712,16 +713,16 @@
           <t>KAS</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>1109671107143</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>820486016949</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>755138283333</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>1316757901639</v>
       </c>
       <c r="F6" s="18" t="n"/>
@@ -753,16 +754,16 @@
           <t>liabilitas</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>10763623250000</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>7477879169492</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>5995004833333</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>5348295737705</v>
       </c>
       <c r="F7" s="18" t="n"/>
@@ -794,16 +795,16 @@
           <t>Utang Bank SAJA Jangka Pendek + Panjang jatuh tempo</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2660909553571</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="18" t="n"/>
@@ -835,16 +836,16 @@
           <t>ekuitas</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>6455841660714</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>6238533576271</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>6348271750000</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>6330880819672</v>
       </c>
       <c r="F9" s="18" t="n"/>
@@ -876,16 +877,16 @@
           <t>laba bersih</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>-265667410714</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="19" t="n">
         <v>-185260135593</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>-458205166667</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>-365231213115</v>
       </c>
       <c r="F10" s="18" t="n"/>
@@ -917,16 +918,16 @@
           <t>pendapatan dari kontrak dengan pelanggan</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>551024821429</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>44825322034</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>2199400000</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>1859622951</v>
       </c>
       <c r="F11" s="18" t="n"/>
@@ -958,16 +959,16 @@
           <t>kas dari aktivitas operasi</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>-456830375000</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>-421878440678</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>-317847850000</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>-314196114754</v>
       </c>
       <c r="F12" s="18" t="n"/>
@@ -999,17 +1000,17 @@
           <t>total share</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>14731366060</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>14731366060</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>20006577715</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>16181071294</v>
+      <c r="D13" s="19" t="n">
+        <v>14731366060</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>14731366060</v>
       </c>
       <c r="F13" s="18" t="n"/>
       <c r="G13" s="18" t="n"/>
@@ -1041,7 +1042,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>7550</v>
+        <v>7800</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>7000</v>
@@ -1999,214 +2000,174 @@
     </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="C24" s="17" t="n">
-        <v>13717107593220</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>1432792796610</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>820486016949</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>7477879169492</v>
-      </c>
-      <c r="G24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>6238533576271</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>-185260135593</v>
-      </c>
-      <c r="J24" s="17" t="n">
-        <v>44825322034</v>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v>-421878440678</v>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>14731366060.0</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="n">
-        <v>1316757901639</v>
-      </c>
-      <c r="N24" s="17" t="n">
-        <v>5348295737705</v>
-      </c>
-      <c r="O24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="17" t="n">
-        <v>6330880819672</v>
-      </c>
-      <c r="Q24" s="17" t="n">
-        <v>-365231213115</v>
-      </c>
-      <c r="R24" s="17" t="n">
-        <v>1859622951</v>
-      </c>
-      <c r="S24" s="17" t="n">
-        <v>-314196114754</v>
-      </c>
-      <c r="T24" s="17" t="inlineStr">
-        <is>
-          <t>16181071294.0</t>
-        </is>
-      </c>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="17" t="n"/>
+      <c r="P24" s="17" t="n"/>
+      <c r="Q24" s="17" t="n"/>
+      <c r="R24" s="17" t="n"/>
+      <c r="S24" s="17" t="n"/>
+      <c r="T24" s="17" t="n"/>
     </row>
     <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="K26" s="17" t="n">
-        <v>45857963000000</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>24630760000000</v>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>4460703000000</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>11706869000000</v>
-      </c>
-      <c r="O26" s="17" t="n">
-        <v>3480000000000</v>
-      </c>
-      <c r="P26" s="17" t="n">
-        <v>34136370000000</v>
-      </c>
-      <c r="Q26" s="17" t="n">
-        <v>5643863000000</v>
-      </c>
-      <c r="R26" s="17" t="n">
-        <v>70704988000000</v>
-      </c>
-      <c r="S26" s="17" t="n">
-        <v>5773901000000</v>
-      </c>
-      <c r="T26" s="17" t="inlineStr">
-        <is>
-          <t>16398000000.0</t>
-        </is>
-      </c>
+      <c r="K26" s="17" t="n"/>
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="17" t="n"/>
+      <c r="N26" s="17" t="n"/>
+      <c r="O26" s="17" t="n"/>
+      <c r="P26" s="17" t="n"/>
+      <c r="Q26" s="17" t="n"/>
+      <c r="R26" s="17" t="n"/>
+      <c r="S26" s="17" t="n"/>
+      <c r="T26" s="17" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="K27" s="17" t="n">
-        <v>43716001000000</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>22325382000000</v>
-      </c>
-      <c r="M27" s="17" t="n">
-        <v>4186323000000</v>
-      </c>
-      <c r="N27" s="17" t="n">
-        <v>11811932000000</v>
-      </c>
-      <c r="O27" s="17" t="n">
-        <v>4250000000000</v>
-      </c>
-      <c r="P27" s="17" t="n">
-        <v>31885954000000</v>
-      </c>
-      <c r="Q27" s="17" t="n">
-        <v>3365043000000</v>
-      </c>
-      <c r="R27" s="17" t="n">
-        <v>50604542000000</v>
-      </c>
-      <c r="S27" s="17" t="n">
-        <v>4015120000000</v>
-      </c>
-      <c r="T27" s="17" t="inlineStr">
-        <is>
-          <t>16398000000.0</t>
-        </is>
-      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="17" t="n"/>
+      <c r="P27" s="17" t="n"/>
+      <c r="Q27" s="17" t="n"/>
+      <c r="R27" s="17" t="n"/>
+      <c r="S27" s="17" t="n"/>
+      <c r="T27" s="17" t="n"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="K28" s="17" t="n">
-        <v>43149273000000</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>21712537000000</v>
-      </c>
-      <c r="M28" s="17" t="n">
-        <v>3381678000000</v>
-      </c>
-      <c r="N28" s="17" t="n">
-        <v>12714801000000</v>
-      </c>
-      <c r="O28" s="17" t="n">
-        <v>4777353000000</v>
-      </c>
-      <c r="P28" s="17" t="n">
-        <v>30415323000000</v>
-      </c>
-      <c r="Q28" s="17" t="n">
-        <v>1900390000000</v>
-      </c>
-      <c r="R28" s="17" t="n">
-        <v>33061683000000</v>
-      </c>
-      <c r="S28" s="17" t="n">
-        <v>2133968000000</v>
-      </c>
-      <c r="T28" s="17" t="inlineStr">
-        <is>
-          <t>16398000000.0</t>
-        </is>
-      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="17" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="17" t="n"/>
+      <c r="O28" s="17" t="n"/>
+      <c r="P28" s="17" t="n"/>
+      <c r="Q28" s="17" t="n"/>
+      <c r="R28" s="17" t="n"/>
+      <c r="S28" s="17" t="n"/>
+      <c r="T28" s="17" t="n"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="K29" s="17" t="n">
-        <v>43765363000000</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>22408711000000</v>
-      </c>
-      <c r="M29" s="17" t="n">
-        <v>5773705000000</v>
-      </c>
-      <c r="N29" s="17" t="n">
-        <v>11938263000000</v>
-      </c>
-      <c r="O29" s="17" t="n">
-        <v>4400000000000</v>
-      </c>
-      <c r="P29" s="17" t="n">
-        <v>31810990000000</v>
-      </c>
-      <c r="Q29" s="17" t="n">
-        <v>1537031000000</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>17704697000000</v>
-      </c>
-      <c r="S29" s="17" t="n">
-        <v>2598615000000</v>
-      </c>
-      <c r="T29" s="17" t="inlineStr">
-        <is>
-          <t>16398000000.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="17" t="n"/>
+      <c r="O29" s="17" t="n"/>
+      <c r="P29" s="17" t="n"/>
+      <c r="Q29" s="17" t="n"/>
+      <c r="R29" s="17" t="n"/>
+      <c r="S29" s="17" t="n"/>
+      <c r="T29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
     <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+    </row>
     <row r="42" ht="14.25" customHeight="1"/>
     <row r="43" ht="14.25" customHeight="1"/>
     <row r="44" ht="14.25" customHeight="1"/>
